--- a/www/terminologies/ValueSet-jdv-hl7-allergyintolerance-clinical-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-hl7-allergyintolerance-clinical-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251216141838</t>
+    <t>20260220142103</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-16T14:18:38+01:00</t>
+    <t>2026-02-20T14:21:03+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/ValueSet-jdv-hl7-allergyintolerance-clinical-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-hl7-allergyintolerance-clinical-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260220142103</t>
+    <t>20260311144903</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-20T14:21:03+01:00</t>
+    <t>2026-03-11T14:49:03+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/ValueSet-jdv-hl7-allergyintolerance-clinical-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-hl7-allergyintolerance-clinical-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260311144903</t>
+    <t>20260420150249</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T14:49:03+01:00</t>
+    <t>2026-04-20T15:02:49+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/ValueSet-jdv-hl7-allergyintolerance-clinical-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-hl7-allergyintolerance-clinical-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260420150249</t>
+    <t>20260619134042</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:02:49+01:00</t>
+    <t>2026-06-19T13:40:42+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/ValueSet-jdv-hl7-allergyintolerance-clinical-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-hl7-allergyintolerance-clinical-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260619134042</t>
+    <t>20260420150249</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T13:40:42+01:00</t>
+    <t>2026-04-20T15:02:49+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/ValueSet-jdv-hl7-allergyintolerance-clinical-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-hl7-allergyintolerance-clinical-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260619134042</t>
+    <t>20260716085851</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T13:40:42+01:00</t>
+    <t>2026-07-16T08:58:51+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
